--- a/artfynd/A 18694-2024 artfynd.xlsx
+++ b/artfynd/A 18694-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135319478</v>
       </c>
       <c r="B2" t="n">
-        <v>98136</v>
+        <v>98138</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 18694-2024 artfynd.xlsx
+++ b/artfynd/A 18694-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>135319478</v>
+        <v>136090687</v>
       </c>
       <c r="B2" t="n">
-        <v>98138</v>
+        <v>96878</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>547981</v>
+        <v>548192</v>
       </c>
       <c r="R2" t="n">
-        <v>6253982</v>
+        <v>6253962</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,6 +785,235 @@
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136090687</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>136090953</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57979</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Smällbäcksmossen, Smällbäcksmossen, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>548164</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6253973</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Torsås</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Gullabo</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Hörde den där punkten är satt.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Sandra Nilsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Sandra Nilsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136090953</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>135319478</v>
+      </c>
+      <c r="B4" t="n">
+        <v>98138</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Smällbäcksmossen, Smällbäcksmossen, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>547981</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6253982</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Torsås</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Gullabo</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Sandra Nilsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Sandra Nilsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135319478</t>
         </is>
@@ -793,6 +1022,8 @@
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 18694-2024 artfynd.xlsx
+++ b/artfynd/A 18694-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136090687</v>
       </c>
       <c r="B2" t="n">
-        <v>96878</v>
+        <v>96879</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 18694-2024 artfynd.xlsx
+++ b/artfynd/A 18694-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136090687</v>
       </c>
       <c r="B2" t="n">
-        <v>96879</v>
+        <v>96880</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 18694-2024 artfynd.xlsx
+++ b/artfynd/A 18694-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136090687</v>
       </c>
       <c r="B2" t="n">
-        <v>96880</v>
+        <v>96881</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136090953</v>
       </c>
       <c r="B3" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 18694-2024 artfynd.xlsx
+++ b/artfynd/A 18694-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136090687</v>
       </c>
       <c r="B2" t="n">
-        <v>96881</v>
+        <v>96887</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136090953</v>
       </c>
       <c r="B3" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 18694-2024 artfynd.xlsx
+++ b/artfynd/A 18694-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136090687</v>
       </c>
       <c r="B2" t="n">
-        <v>96887</v>
+        <v>96888</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136090953</v>
       </c>
       <c r="B3" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 18694-2024 artfynd.xlsx
+++ b/artfynd/A 18694-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136090687</v>
       </c>
       <c r="B2" t="n">
-        <v>96888</v>
+        <v>96899</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 18694-2024 artfynd.xlsx
+++ b/artfynd/A 18694-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136090687</v>
       </c>
       <c r="B2" t="n">
-        <v>96899</v>
+        <v>96912</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136090953</v>
       </c>
       <c r="B3" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 18694-2024 artfynd.xlsx
+++ b/artfynd/A 18694-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136090687</v>
       </c>
       <c r="B2" t="n">
-        <v>96912</v>
+        <v>96913</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 18694-2024 artfynd.xlsx
+++ b/artfynd/A 18694-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136090687</v>
       </c>
       <c r="B2" t="n">
-        <v>96913</v>
+        <v>96926</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136090953</v>
       </c>
       <c r="B3" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 18694-2024 artfynd.xlsx
+++ b/artfynd/A 18694-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136090687</v>
       </c>
       <c r="B2" t="n">
-        <v>96926</v>
+        <v>96927</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
